--- a/research/traditional_assets/database/data/chile/chile_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_precious_metals.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>0.754</v>
+        <v>-0.363</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,73 +606,64 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="V2">
-        <v>0.003105590062111801</v>
+        <v>0.002424242424242424</v>
       </c>
       <c r="W2">
-        <v>-0.1441682600382409</v>
+        <v>0.06660550458715596</v>
       </c>
       <c r="X2">
-        <v>0.2046952224582323</v>
+        <v>0.2756938228722581</v>
       </c>
       <c r="Y2">
-        <v>-0.3488634824964731</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-0.2534653465346536</v>
+        <v>-0.2090883182851021</v>
       </c>
       <c r="AB2">
-        <v>0.1551656294029527</v>
-      </c>
-      <c r="AC2">
-        <v>-0.4086309759376063</v>
+        <v>0.09178080298952726</v>
       </c>
       <c r="AD2">
-        <v>4.58</v>
+        <v>6.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.58</v>
+        <v>6.6</v>
       </c>
       <c r="AG2">
-        <v>4.57</v>
+        <v>6.596</v>
       </c>
       <c r="AH2">
-        <v>0.5871794871794871</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="AI2">
-        <v>-5.264367816091953</v>
+        <v>6.804123711340208</v>
       </c>
       <c r="AJ2">
-        <v>0.5866495507060333</v>
+        <v>0.7999029832646131</v>
       </c>
       <c r="AK2">
-        <v>-5.193181818181819</v>
+        <v>6.828157349896479</v>
       </c>
       <c r="AL2">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AM2">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AO2">
-        <v>-1.454545454545455</v>
+        <v>-8.600000000000001</v>
       </c>
       <c r="AQ2">
-        <v>-1.454545454545455</v>
+        <v>-8.600000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +683,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.754</v>
+        <v>-0.363</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -701,7 +692,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -710,73 +701,64 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="V3">
-        <v>0.003105590062111801</v>
+        <v>0.002424242424242424</v>
       </c>
       <c r="W3">
-        <v>-0.1441682600382409</v>
+        <v>0.06660550458715596</v>
       </c>
       <c r="X3">
-        <v>0.2046952224582323</v>
+        <v>0.2756938228722581</v>
       </c>
       <c r="Y3">
-        <v>-0.3488634824964731</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>-0.2534653465346536</v>
+        <v>-0.2090883182851021</v>
       </c>
       <c r="AB3">
-        <v>0.1551656294029527</v>
-      </c>
-      <c r="AC3">
-        <v>-0.4086309759376063</v>
+        <v>0.09178080298952726</v>
       </c>
       <c r="AD3">
-        <v>4.58</v>
+        <v>6.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.58</v>
+        <v>6.6</v>
       </c>
       <c r="AG3">
-        <v>4.57</v>
+        <v>6.596</v>
       </c>
       <c r="AH3">
-        <v>0.5871794871794871</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="AI3">
-        <v>-5.264367816091953</v>
+        <v>6.804123711340208</v>
       </c>
       <c r="AJ3">
-        <v>0.5866495507060333</v>
+        <v>0.7999029832646131</v>
       </c>
       <c r="AK3">
-        <v>-5.193181818181819</v>
+        <v>6.828157349896479</v>
       </c>
       <c r="AL3">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AM3">
-        <v>0.08799999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="AO3">
-        <v>-1.454545454545455</v>
+        <v>-8.600000000000001</v>
       </c>
       <c r="AQ3">
-        <v>-1.454545454545455</v>
+        <v>-8.600000000000001</v>
       </c>
     </row>
   </sheetData>
